--- a/artfynd/A 71188-2021 artfynd.xlsx
+++ b/artfynd/A 71188-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 71188-2021 artfynd.xlsx
+++ b/artfynd/A 71188-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>16748536</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599268.1069105589</v>
+        <v>599268</v>
       </c>
       <c r="R2" t="n">
-        <v>6396886.704537717</v>
+        <v>6396887</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,19 +753,9 @@
           <t>2014-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16748541</v>
+        <v>67611884</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599252.4394551812</v>
+        <v>599262</v>
       </c>
       <c r="R3" t="n">
-        <v>6396892.199713178</v>
+        <v>6396865</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,22 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-10-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-10-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,37 +891,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16748545</v>
+        <v>67611885</v>
       </c>
       <c r="B4" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -971,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599287.4294030365</v>
+        <v>599262</v>
       </c>
       <c r="R4" t="n">
-        <v>6396885.041280095</v>
+        <v>6396865</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,27 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-10-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gran!</t>
+          <t>2017-09-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,37 +999,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16748526</v>
+        <v>16748545</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1099,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599261.6867253094</v>
+        <v>599287</v>
       </c>
       <c r="R5" t="n">
-        <v>6396864.62923882</v>
+        <v>6396885</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1132,19 +1077,14 @@
           <t>2014-10-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-10-13</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,12 +1115,7 @@
         <v>16748590</v>
       </c>
       <c r="B6" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,12 +1132,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1222,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599287.4294030365</v>
+        <v>599287</v>
       </c>
       <c r="R6" t="n">
-        <v>6396885.041280095</v>
+        <v>6396885</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1255,19 +1190,9 @@
           <t>2014-10-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-10-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1300,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16748533</v>
+        <v>16748523</v>
       </c>
       <c r="B7" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599264.2155200411</v>
+        <v>599305</v>
       </c>
       <c r="R7" t="n">
-        <v>6396892.489162624</v>
+        <v>6396813</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1383,19 +1303,9 @@
           <t>2014-10-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-10-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,15 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16748523</v>
+        <v>16748526</v>
       </c>
       <c r="B8" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599305.2744117586</v>
+        <v>599262</v>
       </c>
       <c r="R8" t="n">
-        <v>6396812.777649769</v>
+        <v>6396865</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1506,19 +1411,9 @@
           <t>2014-10-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-10-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1546,37 +1441,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67611887</v>
+        <v>16748533</v>
       </c>
       <c r="B9" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1596,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599305.2744117586</v>
+        <v>599264</v>
       </c>
       <c r="R9" t="n">
-        <v>6396812.777649769</v>
+        <v>6396892</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1626,22 +1516,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-09-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-09-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,15 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67611884</v>
+        <v>16748541</v>
       </c>
       <c r="B10" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,21 +1560,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1719,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599261.6867253094</v>
+        <v>599252</v>
       </c>
       <c r="R10" t="n">
-        <v>6396864.62923882</v>
+        <v>6396892</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1749,22 +1624,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-09-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-09-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,15 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>67611885</v>
+        <v>67611887</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,21 +1668,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1842,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599261.6867253094</v>
+        <v>599305</v>
       </c>
       <c r="R11" t="n">
-        <v>6396864.62923882</v>
+        <v>6396813</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1875,19 +1735,9 @@
           <t>2017-09-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2017-09-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
